--- a/Input/ContasBB.xlsx
+++ b/Input/ContasBB.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pedro\OneDrive\Documentos\RPA Projects\Case CSN\Python\Input\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9AB0516A-EEB6-4B0D-9C75-A359D6F69381}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41814717-E13F-42A1-84A6-94C7F23D3B99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{5C089912-C0A3-4267-A08E-24A496699FEF}"/>
+    <workbookView xWindow="3510" yWindow="3510" windowWidth="21600" windowHeight="11295" xr2:uid="{5C089912-C0A3-4267-A08E-24A496699FEF}"/>
   </bookViews>
   <sheets>
     <sheet name="INFO_CONTAS" sheetId="1" r:id="rId1"/>
@@ -89,8 +89,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -431,8 +432,7 @@
     <col min="1" max="1" width="8" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="7" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="10" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="8.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="10.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -462,6 +462,12 @@
       <c r="C2">
         <v>26968930</v>
       </c>
+      <c r="D2" s="1">
+        <v>45990</v>
+      </c>
+      <c r="E2" s="1">
+        <v>45996</v>
+      </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3">
